--- a/data/derived/Monitoring_CPUE_data.xlsx
+++ b/data/derived/Monitoring_CPUE_data.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:HI61"/>
+  <dimension ref="A1:HJ61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="9" max="9" width="20.7109375" style="2" customWidth="1"/>
@@ -1450,6 +1450,11 @@
           <t>Substrate_index</t>
         </is>
       </c>
+      <c r="HJ1" s="1" t="inlineStr">
+        <is>
+          <t>Substrate_CV</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1864,6 +1869,9 @@
       <c r="HI2">
         <v>2.8</v>
       </c>
+      <c r="HJ2">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -2354,6 +2362,9 @@
       <c r="HI3">
         <v>4.6</v>
       </c>
+      <c r="HJ3">
+        <v>1.754992877478424</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -2836,6 +2847,9 @@
       <c r="HI4">
         <v>3.4</v>
       </c>
+      <c r="HJ4">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -3280,6 +3294,9 @@
       <c r="HI5">
         <v>3</v>
       </c>
+      <c r="HJ5">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -3749,6 +3766,9 @@
       <c r="HI6">
         <v>3.5</v>
       </c>
+      <c r="HJ6">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -4205,6 +4225,9 @@
       <c r="HI7">
         <v>6.299999999999999</v>
       </c>
+      <c r="HJ7">
+        <v>1.609347693943108</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -4626,6 +4649,9 @@
       <c r="HI8">
         <v>3</v>
       </c>
+      <c r="HJ8">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -5065,6 +5091,9 @@
       <c r="HI9">
         <v>4.6</v>
       </c>
+      <c r="HJ9">
+        <v>1.754992877478424</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -5546,6 +5575,9 @@
       <c r="HI10">
         <v>3.5</v>
       </c>
+      <c r="HJ10">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -5960,6 +5992,9 @@
       <c r="HI11">
         <v>3.2</v>
       </c>
+      <c r="HJ11">
+        <v>2.494827983382154</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -6399,6 +6434,9 @@
       <c r="HI12">
         <v>3</v>
       </c>
+      <c r="HJ12">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -6808,6 +6846,9 @@
       <c r="HI13">
         <v>3</v>
       </c>
+      <c r="HJ13">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -7276,6 +7317,9 @@
       <c r="HI14">
         <v>5.2</v>
       </c>
+      <c r="HJ14">
+        <v>1.80092568789868</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -7771,6 +7815,9 @@
       <c r="HI15">
         <v>3.4</v>
       </c>
+      <c r="HJ15">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -8218,6 +8265,9 @@
       <c r="HI16">
         <v>8</v>
       </c>
+      <c r="HJ16">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -8683,6 +8733,9 @@
       <c r="HI17">
         <v>3</v>
       </c>
+      <c r="HJ17">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -9178,6 +9231,9 @@
       <c r="HI18">
         <v>7.000000000000001</v>
       </c>
+      <c r="HJ18">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -9673,6 +9729,9 @@
       <c r="HI19">
         <v>3.1</v>
       </c>
+      <c r="HJ19">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -10138,6 +10197,9 @@
       <c r="HI20">
         <v>2</v>
       </c>
+      <c r="HJ20">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -10636,6 +10698,9 @@
       <c r="HI21">
         <v>2</v>
       </c>
+      <c r="HJ21">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -11118,6 +11183,9 @@
       <c r="HI22">
         <v>3.1</v>
       </c>
+      <c r="HJ22">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -11583,6 +11651,9 @@
       <c r="HI23">
         <v>3.05</v>
       </c>
+      <c r="HJ23">
+        <v>2.494827983382154</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -12063,6 +12134,9 @@
       <c r="HI24">
         <v>3.9</v>
       </c>
+      <c r="HJ24">
+        <v>1.889444362769118</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -12517,6 +12591,9 @@
       <c r="HI25">
         <v>3.3</v>
       </c>
+      <c r="HJ25">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -13008,6 +13085,9 @@
       <c r="HI26">
         <v>3.1</v>
       </c>
+      <c r="HJ26">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -13468,6 +13548,9 @@
       <c r="HI27">
         <v>2</v>
       </c>
+      <c r="HJ27">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -13954,6 +14037,9 @@
       <c r="HI28">
         <v>2.8</v>
       </c>
+      <c r="HJ28">
+        <v>2.094437076320668</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -14397,6 +14483,9 @@
       <c r="HI29">
         <v>3</v>
       </c>
+      <c r="HJ29">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -14843,6 +14932,9 @@
       <c r="HI30">
         <v>2</v>
       </c>
+      <c r="HJ30">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -15279,6 +15371,9 @@
       <c r="HI31">
         <v>2</v>
       </c>
+      <c r="HJ31">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -15731,6 +15826,9 @@
       <c r="HI32">
         <v>4.3</v>
       </c>
+      <c r="HJ32">
+        <v>1.80092568789868</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -16202,6 +16300,9 @@
       <c r="HI33">
         <v>2.05</v>
       </c>
+      <c r="HJ33">
+        <v>2.494827983382154</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -16643,6 +16744,9 @@
       <c r="HI34">
         <v>2</v>
       </c>
+      <c r="HJ34">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -17079,6 +17183,9 @@
       <c r="HI35">
         <v>2.1</v>
       </c>
+      <c r="HJ35">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -17557,6 +17664,9 @@
       <c r="HI36">
         <v>4.9</v>
       </c>
+      <c r="HJ36">
+        <v>1.268857754044952</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -18031,6 +18141,9 @@
       <c r="HI37">
         <v>3</v>
       </c>
+      <c r="HJ37">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -18486,6 +18599,9 @@
       <c r="HI38">
         <v>3</v>
       </c>
+      <c r="HJ38">
+        <v>2.055075018906447</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -18932,6 +19048,9 @@
       <c r="HI39">
         <v>5</v>
       </c>
+      <c r="HJ39">
+        <v>1.707825127659933</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -19404,6 +19523,9 @@
       <c r="HI40">
         <v>3</v>
       </c>
+      <c r="HJ40">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -19852,6 +19974,9 @@
       <c r="HI41">
         <v>2</v>
       </c>
+      <c r="HJ41">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -20315,6 +20440,9 @@
       <c r="HI42">
         <v>2.2</v>
       </c>
+      <c r="HJ42">
+        <v>2.094437076320668</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -20754,6 +20882,9 @@
       <c r="HI43">
         <v>6.2</v>
       </c>
+      <c r="HJ43">
+        <v>2.094437076320668</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -21235,6 +21366,9 @@
       <c r="HI44">
         <v>3.65</v>
       </c>
+      <c r="HJ44">
+        <v>1.596610994158147</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -21711,6 +21845,9 @@
       <c r="HI45">
         <v>2</v>
       </c>
+      <c r="HJ45">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -22169,6 +22306,9 @@
       <c r="HI46">
         <v>5.4</v>
       </c>
+      <c r="HJ46">
+        <v>1.754992877478424</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -22629,6 +22769,9 @@
       <c r="HI47">
         <v>3.05</v>
       </c>
+      <c r="HJ47">
+        <v>2.494827983382154</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -23077,6 +23220,9 @@
       <c r="HI48">
         <v>3.5</v>
       </c>
+      <c r="HJ48">
+        <v>1.707825127659933</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -23555,6 +23701,9 @@
       <c r="HI49">
         <v>3</v>
       </c>
+      <c r="HJ49">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -24010,6 +24159,9 @@
       <c r="HI50">
         <v>4.2</v>
       </c>
+      <c r="HJ50">
+        <v>1.889444362769118</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -24477,6 +24629,9 @@
       <c r="HI51">
         <v>2.9</v>
       </c>
+      <c r="HJ51">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -24932,6 +25087,9 @@
       <c r="HI52">
         <v>2</v>
       </c>
+      <c r="HJ52">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -25336,6 +25494,9 @@
       <c r="HI53">
         <v>1</v>
       </c>
+      <c r="HJ53">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -25778,6 +25939,9 @@
       <c r="HI54">
         <v>4.2</v>
       </c>
+      <c r="HJ54">
+        <v>1.889444362769118</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -26278,6 +26442,9 @@
       <c r="HI55">
         <v>2</v>
       </c>
+      <c r="HJ55">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -26775,6 +26942,9 @@
       <c r="HI56">
         <v>2.5</v>
       </c>
+      <c r="HJ56">
+        <v>1.707825127659933</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -27247,6 +27417,9 @@
       <c r="HI57">
         <v>1.1</v>
       </c>
+      <c r="HJ57">
+        <v>2.351595203260969</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -27684,6 +27857,9 @@
       <c r="HI58">
         <v>6.2</v>
       </c>
+      <c r="HJ58">
+        <v>2.094437076320668</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -28154,6 +28330,9 @@
       <c r="HI59">
         <v>3.2</v>
       </c>
+      <c r="HJ59">
+        <v>2.494827983382154</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -28597,6 +28776,9 @@
       <c r="HI60">
         <v>2</v>
       </c>
+      <c r="HJ60">
+        <v>2.64575131106459</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -29105,6 +29287,9 @@
       </c>
       <c r="HI61">
         <v>3</v>
+      </c>
+      <c r="HJ61">
+        <v>2.64575131106459</v>
       </c>
     </row>
   </sheetData>

--- a/data/derived/Monitoring_CPUE_data.xlsx
+++ b/data/derived/Monitoring_CPUE_data.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Sructure</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">

--- a/data/derived/Monitoring_CPUE_data.xlsx
+++ b/data/derived/Monitoring_CPUE_data.xlsx
@@ -15,9 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss UTC"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -56,13 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -360,8 +358,7 @@
   <dimension ref="A1:HJ61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="9" max="9" width="20.7109375" style="2" customWidth="1"/>
-    <col min="209" max="209" width="20.7109375" style="3" customWidth="1"/>
+    <col min="209" max="209" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1484,8 +1481,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I2" s="2">
-        <v>45708.57638888889</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-02-20 13:50:00</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1511,7 +1510,7 @@
         <v>663.554783619257</v>
       </c>
       <c r="Q2">
-        <v>0.007535172865047061</v>
+        <v>0.00753517286504706</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -1834,7 +1833,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA2" s="3">
+      <c r="HA2" s="2">
         <v>45708</v>
       </c>
       <c r="HB2" t="inlineStr">
@@ -1857,9 +1856,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG2">
-        <v>1740059400</v>
       </c>
       <c r="HH2" t="inlineStr">
         <is>
@@ -1901,8 +1897,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I3" s="2">
-        <v>45708.48958333333</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-02-20 11:45:00</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1928,7 +1926,7 @@
         <v>104.987389019756</v>
       </c>
       <c r="Q3">
-        <v>0.04762476757145685</v>
+        <v>0.0476247675714568</v>
       </c>
       <c r="S3">
         <v>80632851.42036811</v>
@@ -2327,7 +2325,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA3" s="3">
+      <c r="HA3" s="2">
         <v>45708</v>
       </c>
       <c r="HB3" t="inlineStr">
@@ -2350,9 +2348,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG3">
-        <v>1740051900</v>
       </c>
       <c r="HH3" t="inlineStr">
         <is>
@@ -2394,8 +2389,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I4" s="2">
-        <v>45708.45833333333</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-02-20 11:00:00</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2421,7 +2418,7 @@
         <v>333.12002096304</v>
       </c>
       <c r="Q4">
-        <v>0.01500960520338931</v>
+        <v>0.0150096052033893</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2812,7 +2809,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA4" s="3">
+      <c r="HA4" s="2">
         <v>45708</v>
       </c>
       <c r="HB4" t="inlineStr">
@@ -2835,9 +2832,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG4">
-        <v>1740049200</v>
       </c>
       <c r="HH4" t="inlineStr">
         <is>
@@ -2879,8 +2873,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I5" s="2">
-        <v>45708.41666666667</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-02-20 10:00:00</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2906,7 +2902,7 @@
         <v>881.75332127199</v>
       </c>
       <c r="Q5">
-        <v>0.005670520177669595</v>
+        <v>0.0056705201776696</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -3259,7 +3255,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA5" s="3">
+      <c r="HA5" s="2">
         <v>45708</v>
       </c>
       <c r="HB5" t="inlineStr">
@@ -3282,9 +3278,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG5">
-        <v>1740045600</v>
       </c>
       <c r="HH5" t="inlineStr">
         <is>
@@ -3326,8 +3319,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I6" s="2">
-        <v>45708.59722222222</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-02-20 14:20:00</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3353,7 +3348,7 @@
         <v>797.286203279315</v>
       </c>
       <c r="Q6">
-        <v>0.006271273702510489</v>
+        <v>0.00627127370251049</v>
       </c>
       <c r="S6">
         <v>80632851.42036811</v>
@@ -3731,7 +3726,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA6" s="3">
+      <c r="HA6" s="2">
         <v>45708</v>
       </c>
       <c r="HB6" t="inlineStr">
@@ -3754,9 +3749,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG6">
-        <v>1740061200</v>
       </c>
       <c r="HH6" t="inlineStr">
         <is>
@@ -3798,8 +3790,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I7" s="2">
-        <v>45708.51041666667</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-02-20 12:15:00</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -3825,7 +3819,7 @@
         <v>30.5623995446806</v>
       </c>
       <c r="Q7">
-        <v>0.1635997197370012</v>
+        <v>0.163599719737001</v>
       </c>
       <c r="S7">
         <v>80632851.42036811</v>
@@ -4190,7 +4184,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA7" s="3">
+      <c r="HA7" s="2">
         <v>45708</v>
       </c>
       <c r="HB7" t="inlineStr">
@@ -4213,9 +4207,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG7">
-        <v>1740053700</v>
       </c>
       <c r="HH7" t="inlineStr">
         <is>
@@ -4257,8 +4248,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I8" s="2">
-        <v>45708.625</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-02-20 15:00:00</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -4284,7 +4277,7 @@
         <v>525.663116324665</v>
       </c>
       <c r="Q8">
-        <v>0.009511795377539581</v>
+        <v>0.009511795377539579</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -4614,7 +4607,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA8" s="3">
+      <c r="HA8" s="2">
         <v>45708</v>
       </c>
       <c r="HB8" t="inlineStr">
@@ -4637,9 +4630,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG8">
-        <v>1740063600</v>
       </c>
       <c r="HH8" t="inlineStr">
         <is>
@@ -4681,8 +4671,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I9" s="2">
-        <v>45708.54166666667</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025-02-20 13:00:00</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -4708,7 +4700,7 @@
         <v>540.424301748185</v>
       </c>
       <c r="Q9">
-        <v>0.009251989564173576</v>
+        <v>0.00925198956417358</v>
       </c>
       <c r="S9">
         <v>80632851.42036811</v>
@@ -5056,7 +5048,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA9" s="3">
+      <c r="HA9" s="2">
         <v>45708</v>
       </c>
       <c r="HB9" t="inlineStr">
@@ -5079,9 +5071,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG9">
-        <v>1740056400</v>
       </c>
       <c r="HH9" t="inlineStr">
         <is>
@@ -5123,8 +5112,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I10" s="2">
-        <v>45708.52083333333</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-02-20 12:30:00</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5150,7 +5141,7 @@
         <v>607.964205515417</v>
       </c>
       <c r="Q10">
-        <v>0.008224168387941728</v>
+        <v>0.00822416838794173</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -5540,7 +5531,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA10" s="3">
+      <c r="HA10" s="2">
         <v>45708</v>
       </c>
       <c r="HB10" t="inlineStr">
@@ -5563,9 +5554,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG10">
-        <v>1740054600</v>
       </c>
       <c r="HH10" t="inlineStr">
         <is>
@@ -5607,8 +5595,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I11" s="2">
-        <v>45708.44791666667</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-02-20 10:45:00</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5634,7 +5624,7 @@
         <v>832.3908279250491</v>
       </c>
       <c r="Q11">
-        <v>0.006006793722684093</v>
+        <v>0.00600679372268409</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -5957,7 +5947,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA11" s="3">
+      <c r="HA11" s="2">
         <v>45708</v>
       </c>
       <c r="HB11" t="inlineStr">
@@ -5980,9 +5970,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG11">
-        <v>1740048300</v>
       </c>
       <c r="HH11" t="inlineStr">
         <is>
@@ -6024,8 +6011,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I12" s="2">
-        <v>45708.40416666667</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-02-20 09:42:00</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -6051,7 +6040,7 @@
         <v>699.19990193821</v>
       </c>
       <c r="Q12">
-        <v>0.007151030751205486</v>
+        <v>0.00715103075120549</v>
       </c>
       <c r="S12">
         <v>80632851.42036811</v>
@@ -6399,7 +6388,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA12" s="3">
+      <c r="HA12" s="2">
         <v>45708</v>
       </c>
       <c r="HB12" t="inlineStr">
@@ -6422,9 +6411,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG12">
-        <v>1740044520</v>
       </c>
       <c r="HH12" t="inlineStr">
         <is>
@@ -6466,8 +6452,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I13" s="2">
-        <v>45708.5625</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025-02-20 13:30:00</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -6493,7 +6481,7 @@
         <v>549.720730064047</v>
       </c>
       <c r="Q13">
-        <v>0.009095527467951697</v>
+        <v>0.009095527467951701</v>
       </c>
       <c r="S13">
         <v>80632851.42036811</v>
@@ -6811,7 +6799,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA13" s="3">
+      <c r="HA13" s="2">
         <v>45708</v>
       </c>
       <c r="HB13" t="inlineStr">
@@ -6834,9 +6822,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG13">
-        <v>1740058200</v>
       </c>
       <c r="HH13" t="inlineStr">
         <is>
@@ -6878,8 +6863,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I14" s="2">
-        <v>45673.54513888889</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2025-01-16 13:05:00</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -6905,7 +6892,7 @@
         <v>187.539175274033</v>
       </c>
       <c r="Q14">
-        <v>0.1066443849439773</v>
+        <v>0.106644384943977</v>
       </c>
       <c r="S14">
         <v>33805828.9569732</v>
@@ -7282,7 +7269,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA14" s="3">
+      <c r="HA14" s="2">
         <v>45673</v>
       </c>
       <c r="HB14" t="inlineStr">
@@ -7305,9 +7292,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG14">
-        <v>1737032700</v>
       </c>
       <c r="HH14" t="inlineStr">
         <is>
@@ -7349,8 +7333,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I15" s="2">
-        <v>45673.58958333333</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2025-01-16 14:09:00</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -7376,7 +7362,7 @@
         <v>120.328662180719</v>
       </c>
       <c r="Q15">
-        <v>0.1662114382187881</v>
+        <v>0.166211438218788</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -7780,7 +7766,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA15" s="3">
+      <c r="HA15" s="2">
         <v>45673</v>
       </c>
       <c r="HB15" t="inlineStr">
@@ -7803,9 +7789,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG15">
-        <v>1737036540</v>
       </c>
       <c r="HH15" t="inlineStr">
         <is>
@@ -7847,8 +7830,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I16" s="2">
-        <v>45672.46875</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2025-01-15 11:15:00</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -7874,7 +7859,7 @@
         <v>127.470750970965</v>
       </c>
       <c r="Q16">
-        <v>0.1568987383196287</v>
+        <v>0.156898738319629</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -8230,7 +8215,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA16" s="3">
+      <c r="HA16" s="2">
         <v>45672</v>
       </c>
       <c r="HB16" t="inlineStr">
@@ -8253,9 +8238,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG16">
-        <v>1736939700</v>
       </c>
       <c r="HH16" t="inlineStr">
         <is>
@@ -8297,8 +8279,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I17" s="2">
-        <v>45672.41666666667</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2025-01-15 10:00:00</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -8324,7 +8308,7 @@
         <v>1089.20462436359</v>
       </c>
       <c r="Q17">
-        <v>0.01836202266556275</v>
+        <v>0.0183620226655627</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -8698,7 +8682,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA17" s="3">
+      <c r="HA17" s="2">
         <v>45672</v>
       </c>
       <c r="HB17" t="inlineStr">
@@ -8721,9 +8705,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG17">
-        <v>1736935200</v>
       </c>
       <c r="HH17" t="inlineStr">
         <is>
@@ -8765,8 +8746,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I18" s="2">
-        <v>45673.5625</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2025-01-16 13:30:00</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -8792,7 +8775,7 @@
         <v>107.901207823091</v>
       </c>
       <c r="Q18">
-        <v>0.1853547370182447</v>
+        <v>0.185354737018245</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -9196,7 +9179,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA18" s="3">
+      <c r="HA18" s="2">
         <v>45673</v>
       </c>
       <c r="HB18" t="inlineStr">
@@ -9219,9 +9202,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG18">
-        <v>1737034200</v>
       </c>
       <c r="HH18" t="inlineStr">
         <is>
@@ -9263,8 +9243,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I19" s="2">
-        <v>45672.52083333333</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2025-01-15 12:30:00</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -9694,7 +9676,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA19" s="3">
+      <c r="HA19" s="2">
         <v>45672</v>
       </c>
       <c r="HB19" t="inlineStr">
@@ -9717,9 +9699,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG19">
-        <v>1736944200</v>
       </c>
       <c r="HH19" t="inlineStr">
         <is>
@@ -9761,8 +9740,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I20" s="2">
-        <v>45673.51180555555</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2025-01-16 12:17:00</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -9788,7 +9769,7 @@
         <v>1087.1160731861</v>
       </c>
       <c r="Q20">
-        <v>0.01839729950950349</v>
+        <v>0.0183972995095035</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -10162,7 +10143,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA20" s="3">
+      <c r="HA20" s="2">
         <v>45673</v>
       </c>
       <c r="HB20" t="inlineStr">
@@ -10185,9 +10166,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG20">
-        <v>1737029820</v>
       </c>
       <c r="HH20" t="inlineStr">
         <is>
@@ -10229,8 +10207,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I21" s="2">
-        <v>45672.45138888889</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2025-01-15 10:50:00</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -10256,7 +10236,7 @@
         <v>471.962074330421</v>
       </c>
       <c r="Q21">
-        <v>0.04237628633269797</v>
+        <v>0.042376286332698</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -10663,7 +10643,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA21" s="3">
+      <c r="HA21" s="2">
         <v>45672</v>
       </c>
       <c r="HB21" t="inlineStr">
@@ -10686,9 +10666,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG21">
-        <v>1736938200</v>
       </c>
       <c r="HH21" t="inlineStr">
         <is>
@@ -10730,8 +10707,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I22" s="2">
-        <v>45673.61944444444</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2025-01-16 14:52:00</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -10757,7 +10736,7 @@
         <v>174.996338543086</v>
       </c>
       <c r="Q22">
-        <v>0.1142881054912802</v>
+        <v>0.11428810549128</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -11148,7 +11127,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA22" s="3">
+      <c r="HA22" s="2">
         <v>45673</v>
       </c>
       <c r="HB22" t="inlineStr">
@@ -11171,9 +11150,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG22">
-        <v>1737039120</v>
       </c>
       <c r="HH22" t="inlineStr">
         <is>
@@ -11215,8 +11191,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I23" s="2">
-        <v>45672.43055555555</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2025-01-15 10:20:00</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -11242,7 +11220,7 @@
         <v>1366.67904264963</v>
       </c>
       <c r="Q23">
-        <v>0.01463401382172751</v>
+        <v>0.0146340138217275</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -11616,7 +11594,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA23" s="3">
+      <c r="HA23" s="2">
         <v>45672</v>
       </c>
       <c r="HB23" t="inlineStr">
@@ -11639,9 +11617,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG23">
-        <v>1736936400</v>
       </c>
       <c r="HH23" t="inlineStr">
         <is>
@@ -11683,8 +11658,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I24" s="2">
-        <v>45673.52777777778</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2025-01-16 12:40:00</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -11710,7 +11687,7 @@
         <v>56.312002703404</v>
       </c>
       <c r="Q24">
-        <v>0.3551640687570684</v>
+        <v>0.355164068757068</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -12099,7 +12076,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA24" s="3">
+      <c r="HA24" s="2">
         <v>45673</v>
       </c>
       <c r="HB24" t="inlineStr">
@@ -12122,9 +12099,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG24">
-        <v>1737031200</v>
       </c>
       <c r="HH24" t="inlineStr">
         <is>
@@ -12166,8 +12140,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I25" s="2">
-        <v>45672.49791666667</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2025-01-15 11:57:00</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -12193,7 +12169,7 @@
         <v>259.786453789301</v>
       </c>
       <c r="Q25">
-        <v>0.07698630820920685</v>
+        <v>0.07698630820920679</v>
       </c>
       <c r="S25">
         <v>33805828.9569732</v>
@@ -12556,7 +12532,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA25" s="3">
+      <c r="HA25" s="2">
         <v>45672</v>
       </c>
       <c r="HB25" t="inlineStr">
@@ -12579,9 +12555,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG25">
-        <v>1736942220</v>
       </c>
       <c r="HH25" t="inlineStr">
         <is>
@@ -12623,8 +12596,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I26" s="2">
-        <v>45636.44791666667</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2024-12-10 10:45:00</t>
+        </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -12879,7 +12854,7 @@
         <v>25.72</v>
       </c>
       <c r="DG26">
-        <v>19.03513513513514</v>
+        <v>19.03513513513513</v>
       </c>
       <c r="DH26">
         <v>71.95454545454545</v>
@@ -12945,7 +12920,7 @@
         <v>31.35</v>
       </c>
       <c r="FI26">
-        <v>1.242424242424242</v>
+        <v>1.24242424242424</v>
       </c>
       <c r="FJ26">
         <v>1</v>
@@ -13050,7 +13025,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA26" s="3">
+      <c r="HA26" s="2">
         <v>45636</v>
       </c>
       <c r="HB26" t="inlineStr">
@@ -13073,9 +13048,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG26">
-        <v>1733827500</v>
       </c>
       <c r="HH26" t="inlineStr">
         <is>
@@ -13117,8 +13089,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I27" s="2">
-        <v>45636.47916666667</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2024-12-10 11:30:00</t>
+        </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -13141,7 +13115,7 @@
         <v>29.608065140077</v>
       </c>
       <c r="Q27">
-        <v>0.1688729059580486</v>
+        <v>0.168872905958049</v>
       </c>
       <c r="S27">
         <v>7926889.28599053</v>
@@ -13513,7 +13487,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA27" s="3">
+      <c r="HA27" s="2">
         <v>45636</v>
       </c>
       <c r="HB27" t="inlineStr">
@@ -13536,9 +13510,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG27">
-        <v>1733830200</v>
       </c>
       <c r="HH27" t="inlineStr">
         <is>
@@ -13580,8 +13551,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I28" s="2">
-        <v>45636.54166666667</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2024-12-10 13:00:00</t>
+        </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -14002,7 +13975,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA28" s="3">
+      <c r="HA28" s="2">
         <v>45636</v>
       </c>
       <c r="HB28" t="inlineStr">
@@ -14025,9 +13998,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG28">
-        <v>1733835600</v>
       </c>
       <c r="HH28" t="inlineStr">
         <is>
@@ -14069,8 +14039,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I29" s="2">
-        <v>45637.72916666667</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2024-12-11 17:30:00</t>
+        </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -14093,7 +14065,7 @@
         <v>131.908502903605</v>
       </c>
       <c r="Q29">
-        <v>0.03790506214488582</v>
+        <v>0.0379050621448858</v>
       </c>
       <c r="S29">
         <v>7926889.28599053</v>
@@ -14448,7 +14420,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA29" s="3">
+      <c r="HA29" s="2">
         <v>45637</v>
       </c>
       <c r="HB29" t="inlineStr">
@@ -14471,9 +14443,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG29">
-        <v>1733938200</v>
       </c>
       <c r="HH29" t="inlineStr">
         <is>
@@ -14515,8 +14484,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I30" s="2">
-        <v>45636.51180555555</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2024-12-10 12:17:00</t>
+        </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -14539,7 +14510,7 @@
         <v>170.312698842019</v>
       </c>
       <c r="Q30">
-        <v>0.02935776388957332</v>
+        <v>0.0293577638895733</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -14897,7 +14868,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA30" s="3">
+      <c r="HA30" s="2">
         <v>45636</v>
       </c>
       <c r="HB30" t="inlineStr">
@@ -14920,9 +14891,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG30">
-        <v>1733833020</v>
       </c>
       <c r="HH30" t="inlineStr">
         <is>
@@ -14964,8 +14932,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I31" s="2">
-        <v>45636.53125</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2024-12-10 12:45:00</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -14988,7 +14958,7 @@
         <v>84.527911993492</v>
       </c>
       <c r="Q31">
-        <v>0.05915205855771005</v>
+        <v>0.05915205855771</v>
       </c>
       <c r="S31">
         <v>7926889.28599053</v>
@@ -15336,7 +15306,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA31" s="3">
+      <c r="HA31" s="2">
         <v>45636</v>
       </c>
       <c r="HB31" t="inlineStr">
@@ -15359,9 +15329,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG31">
-        <v>1733834700</v>
       </c>
       <c r="HH31" t="inlineStr">
         <is>
@@ -15403,8 +15370,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I32" s="2">
-        <v>45637.66319444445</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2024-12-11 15:55:00</t>
+        </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -15427,7 +15396,7 @@
         <v>60.7338903342372</v>
       </c>
       <c r="Q32">
-        <v>0.08232635802652306</v>
+        <v>0.08232635802652311</v>
       </c>
       <c r="S32">
         <v>7926889.28599053</v>
@@ -15791,7 +15760,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA32" s="3">
+      <c r="HA32" s="2">
         <v>45637</v>
       </c>
       <c r="HB32" t="inlineStr">
@@ -15814,9 +15783,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG32">
-        <v>1733932500</v>
       </c>
       <c r="HH32" t="inlineStr">
         <is>
@@ -15858,8 +15824,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I33" s="2">
-        <v>45637.70833333333</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2024-12-11 17:00:00</t>
+        </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -15882,7 +15850,7 @@
         <v>241.86196155345</v>
       </c>
       <c r="Q33">
-        <v>0.02067294901556908</v>
+        <v>0.0206729490155691</v>
       </c>
       <c r="S33">
         <v>7926889.28599053</v>
@@ -16265,7 +16233,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA33" s="3">
+      <c r="HA33" s="2">
         <v>45637</v>
       </c>
       <c r="HB33" t="inlineStr">
@@ -16288,9 +16256,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG33">
-        <v>1733936400</v>
       </c>
       <c r="HH33" t="inlineStr">
         <is>
@@ -16332,8 +16297,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I34" s="2">
-        <v>45636.47222222222</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2024-12-10 11:20:00</t>
+        </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -16356,7 +16323,7 @@
         <v>157.403293407812</v>
       </c>
       <c r="Q34">
-        <v>0.03176553610632297</v>
+        <v>0.031765536106323</v>
       </c>
       <c r="S34">
         <v>7926889.28599053</v>
@@ -16709,7 +16676,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA34" s="3">
+      <c r="HA34" s="2">
         <v>45636</v>
       </c>
       <c r="HB34" t="inlineStr">
@@ -16732,9 +16699,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG34">
-        <v>1733829600</v>
       </c>
       <c r="HH34" t="inlineStr">
         <is>
@@ -16776,8 +16740,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I35" s="2">
-        <v>45637.65138888889</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2024-12-11 15:38:00</t>
+        </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -16800,7 +16766,7 @@
         <v>73.8193002366027</v>
       </c>
       <c r="Q35">
-        <v>0.06773296392642843</v>
+        <v>0.0677329639264284</v>
       </c>
       <c r="S35">
         <v>7926889.28599053</v>
@@ -17148,7 +17114,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA35" s="3">
+      <c r="HA35" s="2">
         <v>45637</v>
       </c>
       <c r="HB35" t="inlineStr">
@@ -17171,9 +17137,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG35">
-        <v>1733931480</v>
       </c>
       <c r="HH35" t="inlineStr">
         <is>
@@ -17215,8 +17178,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I36" s="2">
-        <v>45637.67638888889</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2024-12-11 16:14:00</t>
+        </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -17629,7 +17594,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA36" s="3">
+      <c r="HA36" s="2">
         <v>45637</v>
       </c>
       <c r="HB36" t="inlineStr">
@@ -17652,9 +17617,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG36">
-        <v>1733933640</v>
       </c>
       <c r="HH36" t="inlineStr">
         <is>
@@ -17696,8 +17658,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I37" s="2">
-        <v>45637.69722222222</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2024-12-11 16:44:00</t>
+        </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -18106,7 +18070,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA37" s="3">
+      <c r="HA37" s="2">
         <v>45637</v>
       </c>
       <c r="HB37" t="inlineStr">
@@ -18129,9 +18093,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG37">
-        <v>1733935440</v>
       </c>
       <c r="HH37" t="inlineStr">
         <is>
@@ -18173,8 +18134,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I38" s="2">
-        <v>45602.46875</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2024-11-06 11:15:00</t>
+        </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -18200,7 +18163,7 @@
         <v>126.009846508404</v>
       </c>
       <c r="Q38">
-        <v>0.1587177554308515</v>
+        <v>0.158717755430851</v>
       </c>
       <c r="S38">
         <v>11137002.6670586</v>
@@ -18564,7 +18527,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA38" s="3">
+      <c r="HA38" s="2">
         <v>45602</v>
       </c>
       <c r="HB38" t="inlineStr">
@@ -18587,9 +18550,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG38">
-        <v>1730891700</v>
       </c>
       <c r="HH38" t="inlineStr">
         <is>
@@ -18631,8 +18591,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I39" s="2">
-        <v>45602.51041666667</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2024-11-06 12:15:00</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -18658,7 +18620,7 @@
         <v>48.7136423915966</v>
       </c>
       <c r="Q39">
-        <v>0.4105626066559565</v>
+        <v>0.410562606655956</v>
       </c>
       <c r="S39">
         <v>11137002.6670586</v>
@@ -19013,7 +18975,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA39" s="3">
+      <c r="HA39" s="2">
         <v>45602</v>
       </c>
       <c r="HB39" t="inlineStr">
@@ -19036,9 +18998,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG39">
-        <v>1730895300</v>
       </c>
       <c r="HH39" t="inlineStr">
         <is>
@@ -19080,8 +19039,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I40" s="2">
-        <v>45602.38194444445</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2024-11-06 09:10:00</t>
+        </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -19107,7 +19068,7 @@
         <v>146.786508891309</v>
       </c>
       <c r="Q40">
-        <v>0.1362523037781994</v>
+        <v>0.136252303778199</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -19488,7 +19449,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA40" s="3">
+      <c r="HA40" s="2">
         <v>45602</v>
       </c>
       <c r="HB40" t="inlineStr">
@@ -19511,9 +19472,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG40">
-        <v>1730884200</v>
       </c>
       <c r="HH40" t="inlineStr">
         <is>
@@ -19555,8 +19513,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I41" s="2">
-        <v>45603.60416666667</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2024-11-07 14:30:00</t>
+        </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -19582,7 +19542,7 @@
         <v>763.788283079701</v>
       </c>
       <c r="Q41">
-        <v>0.02618526683776453</v>
+        <v>0.0261852668377645</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -19771,7 +19731,7 @@
         <v>0</v>
       </c>
       <c r="CF41">
-        <v>40.75</v>
+        <v>40.74999999999998</v>
       </c>
       <c r="CG41">
         <v>23.5</v>
@@ -19798,7 +19758,7 @@
         <v>0</v>
       </c>
       <c r="CO41">
-        <v>163</v>
+        <v>162.9999999999999</v>
       </c>
       <c r="CP41">
         <v>94</v>
@@ -19810,7 +19770,7 @@
         <v>160</v>
       </c>
       <c r="DG41">
-        <v>4.183333333333334</v>
+        <v>4.183333333333332</v>
       </c>
       <c r="DH41">
         <v>94</v>
@@ -19822,7 +19782,7 @@
         <v>1</v>
       </c>
       <c r="DY41">
-        <v>163</v>
+        <v>162.9999999999999</v>
       </c>
       <c r="DZ41">
         <v>94</v>
@@ -19846,7 +19806,7 @@
         <v>160</v>
       </c>
       <c r="FI41">
-        <v>2.113636363636364</v>
+        <v>2.11363636363636</v>
       </c>
       <c r="FJ41">
         <v>94</v>
@@ -19939,7 +19899,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA41" s="3">
+      <c r="HA41" s="2">
         <v>45603</v>
       </c>
       <c r="HB41" t="inlineStr">
@@ -19962,9 +19922,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG41">
-        <v>1730989800</v>
       </c>
       <c r="HH41" t="inlineStr">
         <is>
@@ -20006,8 +19963,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I42" s="2">
-        <v>45602.44791666667</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2024-11-06 10:45:00</t>
+        </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -20033,7 +19992,7 @@
         <v>197.479843716441</v>
       </c>
       <c r="Q42">
-        <v>0.1012761587391054</v>
+        <v>0.101276158739105</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -20405,7 +20364,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA42" s="3">
+      <c r="HA42" s="2">
         <v>45602</v>
       </c>
       <c r="HB42" t="inlineStr">
@@ -20428,9 +20387,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG42">
-        <v>1730889900</v>
       </c>
       <c r="HH42" t="inlineStr">
         <is>
@@ -20472,8 +20428,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I43" s="2">
-        <v>45602.43055555555</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2024-11-06 10:20:00</t>
+        </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -20499,7 +20457,7 @@
         <v>74.72167756969409</v>
       </c>
       <c r="Q43">
-        <v>0.2676599435464452</v>
+        <v>0.267659943546445</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -20847,7 +20805,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA43" s="3">
+      <c r="HA43" s="2">
         <v>45602</v>
       </c>
       <c r="HB43" t="inlineStr">
@@ -20870,9 +20828,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG43">
-        <v>1730888400</v>
       </c>
       <c r="HH43" t="inlineStr">
         <is>
@@ -20914,8 +20869,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I44" s="2">
-        <v>45603.64583333333</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2024-11-07 15:30:00</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -20941,7 +20898,7 @@
         <v>109.241631729059</v>
       </c>
       <c r="Q44">
-        <v>0.1830803850459135</v>
+        <v>0.183080385045913</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -21157,7 +21114,7 @@
         <v>0</v>
       </c>
       <c r="CO44">
-        <v>745</v>
+        <v>745.0000000000001</v>
       </c>
       <c r="CQ44">
         <v>77.38422243090879</v>
@@ -21196,7 +21153,7 @@
         <v>1</v>
       </c>
       <c r="DY44">
-        <v>745</v>
+        <v>745.0000000000001</v>
       </c>
       <c r="EA44">
         <v>77.38422243090879</v>
@@ -21238,7 +21195,7 @@
         <v>800</v>
       </c>
       <c r="FI44">
-        <v>2.111111111111111</v>
+        <v>2.11111111111111</v>
       </c>
       <c r="FK44">
         <v>9</v>
@@ -21331,7 +21288,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA44" s="3">
+      <c r="HA44" s="2">
         <v>45603</v>
       </c>
       <c r="HB44" t="inlineStr">
@@ -21354,9 +21311,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG44">
-        <v>1730993400</v>
       </c>
       <c r="HH44" t="inlineStr">
         <is>
@@ -21398,8 +21352,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I45" s="2">
-        <v>45603.58333333333</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2024-11-07 14:00:00</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -21425,7 +21381,7 @@
         <v>938.877215347447</v>
       </c>
       <c r="Q45">
-        <v>0.02130204000381314</v>
+        <v>0.0213020400038131</v>
       </c>
       <c r="S45">
         <v>11137002.6670586</v>
@@ -21810,7 +21766,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA45" s="3">
+      <c r="HA45" s="2">
         <v>45603</v>
       </c>
       <c r="HB45" t="inlineStr">
@@ -21833,9 +21789,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG45">
-        <v>1730988000</v>
       </c>
       <c r="HH45" t="inlineStr">
         <is>
@@ -21877,8 +21830,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I46" s="2">
-        <v>45602.49305555555</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2024-11-06 11:50:00</t>
+        </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -21904,7 +21859,7 @@
         <v>214.645988148536</v>
       </c>
       <c r="Q46">
-        <v>0.09317667743298286</v>
+        <v>0.0931766774329829</v>
       </c>
       <c r="S46">
         <v>11137002.6670586</v>
@@ -22271,7 +22226,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA46" s="3">
+      <c r="HA46" s="2">
         <v>45602</v>
       </c>
       <c r="HB46" t="inlineStr">
@@ -22294,9 +22249,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG46">
-        <v>1730893800</v>
       </c>
       <c r="HH46" t="inlineStr">
         <is>
@@ -22338,8 +22290,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I47" s="2">
-        <v>45602.40972222222</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2024-11-06 09:50:00</t>
+        </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -22365,7 +22319,7 @@
         <v>180.647588784886</v>
       </c>
       <c r="Q47">
-        <v>0.1107127979649696</v>
+        <v>0.11071279796497</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -22734,7 +22688,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA47" s="3">
+      <c r="HA47" s="2">
         <v>45602</v>
       </c>
       <c r="HB47" t="inlineStr">
@@ -22757,9 +22711,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG47">
-        <v>1730886600</v>
       </c>
       <c r="HH47" t="inlineStr">
         <is>
@@ -22801,8 +22752,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I48" s="2">
-        <v>45603.65763888889</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2024-11-07 15:47:00</t>
+        </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -22828,7 +22781,7 @@
         <v>186.207468325378</v>
       </c>
       <c r="Q48">
-        <v>0.1074070775993372</v>
+        <v>0.107407077599337</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -23185,7 +23138,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA48" s="3">
+      <c r="HA48" s="2">
         <v>45603</v>
       </c>
       <c r="HB48" t="inlineStr">
@@ -23208,9 +23161,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG48">
-        <v>1730994420</v>
       </c>
       <c r="HH48" t="inlineStr">
         <is>
@@ -23252,8 +23202,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I49" s="2">
-        <v>45603.625</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2024-11-07 15:00:00</t>
+        </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -23279,7 +23231,7 @@
         <v>255.165057668663</v>
       </c>
       <c r="Q49">
-        <v>0.07838063793973862</v>
+        <v>0.0783806379397386</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -23495,7 +23447,7 @@
         <v>0</v>
       </c>
       <c r="CO49">
-        <v>453.2</v>
+        <v>453.1999999999999</v>
       </c>
       <c r="CP49">
         <v>8</v>
@@ -23513,7 +23465,7 @@
         <v>25.35</v>
       </c>
       <c r="DG49">
-        <v>7.715151515151516</v>
+        <v>7.715151515151514</v>
       </c>
       <c r="DH49">
         <v>2</v>
@@ -23531,7 +23483,7 @@
         <v>2</v>
       </c>
       <c r="DY49">
-        <v>453.2</v>
+        <v>453.1999999999999</v>
       </c>
       <c r="DZ49">
         <v>8</v>
@@ -23666,7 +23618,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA49" s="3">
+      <c r="HA49" s="2">
         <v>45603</v>
       </c>
       <c r="HB49" t="inlineStr">
@@ -23689,9 +23641,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG49">
-        <v>1730991600</v>
       </c>
       <c r="HH49" t="inlineStr">
         <is>
@@ -23733,8 +23682,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I50" s="2">
-        <v>45596.50694444445</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2024-10-31 12:10:00</t>
+        </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -23742,7 +23693,7 @@
         </is>
       </c>
       <c r="K50">
-        <v>6.666666666666667</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -23760,7 +23711,7 @@
         <v>91.4282251493164</v>
       </c>
       <c r="Q50">
-        <v>0.2187508285033086</v>
+        <v>0.218750828503309</v>
       </c>
       <c r="S50">
         <v>3434118.08964225</v>
@@ -24124,7 +24075,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA50" s="3">
+      <c r="HA50" s="2">
         <v>45596</v>
       </c>
       <c r="HB50" t="inlineStr">
@@ -24147,9 +24098,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG50">
-        <v>1730376600</v>
       </c>
       <c r="HH50" t="inlineStr">
         <is>
@@ -24191,8 +24139,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I51" s="2">
-        <v>45596.47222222222</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2024-10-31 11:20:00</t>
+        </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -24200,7 +24150,7 @@
         </is>
       </c>
       <c r="K51">
-        <v>6.666666666666667</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="L51">
         <v>1</v>
@@ -24218,7 +24168,7 @@
         <v>332.247986624121</v>
       </c>
       <c r="Q51">
-        <v>0.06019600059345556</v>
+        <v>0.0601960005934556</v>
       </c>
       <c r="S51">
         <v>3434118.08964225</v>
@@ -24594,7 +24544,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA51" s="3">
+      <c r="HA51" s="2">
         <v>45596</v>
       </c>
       <c r="HB51" t="inlineStr">
@@ -24617,9 +24567,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG51">
-        <v>1730373600</v>
       </c>
       <c r="HH51" t="inlineStr">
         <is>
@@ -24661,8 +24608,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I52" s="2">
-        <v>45596.58333333333</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2024-10-31 14:00:00</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -24670,7 +24619,7 @@
         </is>
       </c>
       <c r="K52">
-        <v>6.666666666666667</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -24688,7 +24637,7 @@
         <v>170.208329893393</v>
       </c>
       <c r="Q52">
-        <v>0.1175030623502777</v>
+        <v>0.117503062350278</v>
       </c>
       <c r="S52">
         <v>3434118.08964225</v>
@@ -25052,7 +25001,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA52" s="3">
+      <c r="HA52" s="2">
         <v>45596</v>
       </c>
       <c r="HB52" t="inlineStr">
@@ -25075,9 +25024,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG52">
-        <v>1730383200</v>
       </c>
       <c r="HH52" t="inlineStr">
         <is>
@@ -25119,8 +25065,10 @@
           <t>Muddy</t>
         </is>
       </c>
-      <c r="I53" s="2">
-        <v>45679.43125</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2025-01-22 10:21:00</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -25146,7 +25094,7 @@
         <v>777.172</v>
       </c>
       <c r="Q53">
-        <v>0.02573432908030655</v>
+        <v>0.0257343290803065</v>
       </c>
       <c r="S53">
         <v>3434118.08964225</v>
@@ -25459,7 +25407,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA53" s="3">
+      <c r="HA53" s="2">
         <v>45679</v>
       </c>
       <c r="HB53" t="inlineStr">
@@ -25482,9 +25430,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG53">
-        <v>1737541260</v>
       </c>
       <c r="HH53" t="inlineStr">
         <is>
@@ -25526,8 +25471,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I54" s="2">
-        <v>45679.375</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2025-01-22 09:00:00</t>
+        </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -25553,7 +25500,7 @@
         <v>169.241617628642</v>
       </c>
       <c r="Q54">
-        <v>0.1181742427201621</v>
+        <v>0.118174242720162</v>
       </c>
       <c r="S54">
         <v>3434118.08964225</v>
@@ -25904,7 +25851,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA54" s="3">
+      <c r="HA54" s="2">
         <v>45679</v>
       </c>
       <c r="HB54" t="inlineStr">
@@ -25927,9 +25874,6 @@
         <is>
           <t>Summer</t>
         </is>
-      </c>
-      <c r="HG54">
-        <v>1737536400</v>
       </c>
       <c r="HH54" t="inlineStr">
         <is>
@@ -25971,8 +25915,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I55" s="2">
-        <v>45596.45833333333</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2024-10-31 11:00:00</t>
+        </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -25998,7 +25944,7 @@
         <v>285.328641897722</v>
       </c>
       <c r="Q55">
-        <v>0.07009461043581156</v>
+        <v>0.0700946104358116</v>
       </c>
       <c r="S55">
         <v>3434118.08964225</v>
@@ -26407,7 +26353,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA55" s="3">
+      <c r="HA55" s="2">
         <v>45596</v>
       </c>
       <c r="HB55" t="inlineStr">
@@ -26430,9 +26376,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG55">
-        <v>1730372400</v>
       </c>
       <c r="HH55" t="inlineStr">
         <is>
@@ -26474,8 +26417,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I56" s="2">
-        <v>45596.56944444445</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2024-10-31 13:40:00</t>
+        </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -26483,7 +26428,7 @@
         </is>
       </c>
       <c r="K56">
-        <v>6.666666666666667</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -26501,7 +26446,7 @@
         <v>92.7157039998513</v>
       </c>
       <c r="Q56">
-        <v>0.2157131870565538</v>
+        <v>0.215713187056554</v>
       </c>
       <c r="S56">
         <v>3434118.08964225</v>
@@ -26907,7 +26852,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA56" s="3">
+      <c r="HA56" s="2">
         <v>45596</v>
       </c>
       <c r="HB56" t="inlineStr">
@@ -26930,9 +26875,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG56">
-        <v>1730382000</v>
       </c>
       <c r="HH56" t="inlineStr">
         <is>
@@ -26974,8 +26916,10 @@
           <t>Muddy</t>
         </is>
       </c>
-      <c r="I57" s="2">
-        <v>45596.54861111111</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2024-10-31 13:10:00</t>
+        </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -26983,7 +26927,7 @@
         </is>
       </c>
       <c r="K57">
-        <v>6.666666666666667</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="L57">
         <v>1</v>
@@ -27001,7 +26945,7 @@
         <v>466.526</v>
       </c>
       <c r="Q57">
-        <v>0.04287006511962892</v>
+        <v>0.0428700651196289</v>
       </c>
       <c r="S57">
         <v>3434118.08964225</v>
@@ -27382,7 +27326,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA57" s="3">
+      <c r="HA57" s="2">
         <v>45596</v>
       </c>
       <c r="HB57" t="inlineStr">
@@ -27405,9 +27349,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG57">
-        <v>1730380200</v>
       </c>
       <c r="HH57" t="inlineStr">
         <is>
@@ -27449,8 +27390,10 @@
           <t>Rocky</t>
         </is>
       </c>
-      <c r="I58" s="2">
-        <v>45596.48888888889</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2024-10-31 11:44:00</t>
+        </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -27458,7 +27401,7 @@
         </is>
       </c>
       <c r="K58">
-        <v>6.666666666666667</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -27476,7 +27419,7 @@
         <v>105.815168000486</v>
       </c>
       <c r="Q58">
-        <v>0.1890088196042758</v>
+        <v>0.189008819604276</v>
       </c>
       <c r="S58">
         <v>3434118.08964225</v>
@@ -27822,7 +27765,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA58" s="3">
+      <c r="HA58" s="2">
         <v>45596</v>
       </c>
       <c r="HB58" t="inlineStr">
@@ -27845,9 +27788,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG58">
-        <v>1730375040</v>
       </c>
       <c r="HH58" t="inlineStr">
         <is>
@@ -27889,8 +27829,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I59" s="2">
-        <v>45596.41666666667</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2024-10-31 10:00:00</t>
+        </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -28295,7 +28237,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA59" s="3">
+      <c r="HA59" s="2">
         <v>45596</v>
       </c>
       <c r="HB59" t="inlineStr">
@@ -28318,9 +28260,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG59">
-        <v>1730368800</v>
       </c>
       <c r="HH59" t="inlineStr">
         <is>
@@ -28362,8 +28301,10 @@
           <t>Emergent Macrophyte</t>
         </is>
       </c>
-      <c r="I60" s="2">
-        <v>45596.60416666667</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2024-10-31 14:30:00</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -28371,7 +28312,7 @@
         </is>
       </c>
       <c r="K60">
-        <v>6.666666666666667</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -28389,7 +28330,7 @@
         <v>166.710960104996</v>
       </c>
       <c r="Q60">
-        <v>0.1199681171975965</v>
+        <v>0.119968117197597</v>
       </c>
       <c r="S60">
         <v>3434118.08964225</v>
@@ -28741,7 +28682,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA60" s="3">
+      <c r="HA60" s="2">
         <v>45596</v>
       </c>
       <c r="HB60" t="inlineStr">
@@ -28764,9 +28705,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG60">
-        <v>1730385000</v>
       </c>
       <c r="HH60" t="inlineStr">
         <is>
@@ -28808,8 +28746,10 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="I61" s="2">
-        <v>45596.38194444445</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2024-10-31 09:10:00</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -29253,7 +29193,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="HA61" s="3">
+      <c r="HA61" s="2">
         <v>45596</v>
       </c>
       <c r="HB61" t="inlineStr">
@@ -29276,9 +29216,6 @@
         <is>
           <t>Spring</t>
         </is>
-      </c>
-      <c r="HG61">
-        <v>1730365800</v>
       </c>
       <c r="HH61" t="inlineStr">
         <is>
